--- a/public/assets/templates/Template_Rapbs_Akun.xlsx
+++ b/public/assets/templates/Template_Rapbs_Akun.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_KULIAH\semester2\PBL\Template_Import_SIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB73ED39-A7F3-4BD5-A4B5-F871A9BFC30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291C6A2F-BB80-43EF-9C72-4E6E569CBABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{AC1335BE-EAD5-46A9-BDC0-ECAA1E103BF0}"/>
   </bookViews>
@@ -799,6 +799,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -872,11 +876,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -895,8 +900,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6D3851EE-4553-4B90-8CC1-6308A2F13413}"/>
   </cellStyles>
@@ -1240,7 +1249,7 @@
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="7">
         <v>0</v>
       </c>
       <c r="D2" s="6" t="s">
@@ -1254,7 +1263,7 @@
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="7">
         <v>0</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -1268,7 +1277,7 @@
       <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>0</v>
       </c>
       <c r="D4" s="6" t="s">
@@ -1282,7 +1291,7 @@
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>0</v>
       </c>
       <c r="D5" s="6" t="s">
@@ -1296,7 +1305,7 @@
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>0</v>
       </c>
       <c r="D6" s="6" t="s">
@@ -1310,7 +1319,7 @@
       <c r="B7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>0</v>
       </c>
       <c r="D7" s="6" t="s">
@@ -1324,7 +1333,7 @@
       <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>0</v>
       </c>
       <c r="D8" s="6" t="s">
@@ -1338,7 +1347,7 @@
       <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>0</v>
       </c>
       <c r="D9" s="6" t="s">
@@ -1352,7 +1361,7 @@
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>0</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -1366,7 +1375,7 @@
       <c r="B11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>0</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -1380,7 +1389,7 @@
       <c r="B12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>0</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -1394,7 +1403,7 @@
       <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>0</v>
       </c>
       <c r="D13" s="6" t="s">
@@ -1408,7 +1417,7 @@
       <c r="B14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>0</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -1422,7 +1431,7 @@
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>0</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -1436,7 +1445,7 @@
       <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="7">
         <v>0</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -1450,7 +1459,7 @@
       <c r="B17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="7">
         <v>0</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -1464,7 +1473,7 @@
       <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="7">
         <v>0</v>
       </c>
       <c r="D18" s="6" t="s">
@@ -1478,7 +1487,7 @@
       <c r="B19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>0</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -1492,7 +1501,7 @@
       <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>0</v>
       </c>
       <c r="D20" s="6" t="s">
@@ -1506,7 +1515,7 @@
       <c r="B21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <v>0</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -1520,7 +1529,7 @@
       <c r="B22" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="7">
         <v>0</v>
       </c>
       <c r="D22" s="6" t="s">
@@ -1534,7 +1543,7 @@
       <c r="B23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <v>0</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -1548,7 +1557,7 @@
       <c r="B24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>0</v>
       </c>
       <c r="D24" s="6" t="s">
@@ -1562,7 +1571,7 @@
       <c r="B25" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>0</v>
       </c>
       <c r="D25" s="6" t="s">
@@ -1576,7 +1585,7 @@
       <c r="B26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="7">
         <v>0</v>
       </c>
       <c r="D26" s="6" t="s">
@@ -1590,7 +1599,7 @@
       <c r="B27" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="7">
         <v>0</v>
       </c>
       <c r="D27" s="6" t="s">
@@ -1604,7 +1613,7 @@
       <c r="B28" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <v>0</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -1618,7 +1627,7 @@
       <c r="B29" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
         <v>0</v>
       </c>
       <c r="D29" s="6" t="s">
@@ -1632,7 +1641,7 @@
       <c r="B30" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="7">
         <v>0</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -1646,7 +1655,7 @@
       <c r="B31" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>0</v>
       </c>
       <c r="D31" s="6" t="s">
@@ -1660,7 +1669,7 @@
       <c r="B32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="7">
         <v>0</v>
       </c>
       <c r="D32" s="6" t="s">
@@ -1674,7 +1683,7 @@
       <c r="B33" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="7">
         <v>0</v>
       </c>
       <c r="D33" s="6" t="s">
@@ -1688,7 +1697,7 @@
       <c r="B34" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="7">
         <v>0</v>
       </c>
       <c r="D34" s="6" t="s">
@@ -1702,7 +1711,7 @@
       <c r="B35" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="7">
         <v>0</v>
       </c>
       <c r="D35" s="6" t="s">
@@ -1716,7 +1725,7 @@
       <c r="B36" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="7">
         <v>0</v>
       </c>
       <c r="D36" s="6" t="s">
@@ -1730,7 +1739,7 @@
       <c r="B37" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="7">
         <v>0</v>
       </c>
       <c r="D37" s="6" t="s">
@@ -1744,7 +1753,7 @@
       <c r="B38" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="7">
         <v>0</v>
       </c>
       <c r="D38" s="6" t="s">
@@ -1758,7 +1767,7 @@
       <c r="B39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="7">
         <v>0</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1772,7 +1781,7 @@
       <c r="B40" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40" s="7">
         <v>0</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -1786,7 +1795,7 @@
       <c r="B41" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="7">
         <v>0</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -1800,7 +1809,7 @@
       <c r="B42" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="7">
         <v>0</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -1814,7 +1823,7 @@
       <c r="B43" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="7">
         <v>0</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -1828,7 +1837,7 @@
       <c r="B44" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="7">
         <v>0</v>
       </c>
       <c r="D44" s="6" t="s">
@@ -1842,7 +1851,7 @@
       <c r="B45" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="7">
         <v>0</v>
       </c>
       <c r="D45" s="6" t="s">
@@ -1856,7 +1865,7 @@
       <c r="B46" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="7">
         <v>0</v>
       </c>
       <c r="D46" s="6" t="s">
@@ -1870,7 +1879,7 @@
       <c r="B47" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="7">
         <v>0</v>
       </c>
       <c r="D47" s="6" t="s">
@@ -1884,7 +1893,7 @@
       <c r="B48" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="6">
+      <c r="C48" s="7">
         <v>0</v>
       </c>
       <c r="D48" s="6" t="s">
@@ -1898,7 +1907,7 @@
       <c r="B49" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="7">
         <v>0</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -1912,7 +1921,7 @@
       <c r="B50" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="7">
         <v>0</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -1926,7 +1935,7 @@
       <c r="B51" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="7">
         <v>0</v>
       </c>
       <c r="D51" s="6" t="s">
@@ -1940,7 +1949,7 @@
       <c r="B52" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C52" s="6">
+      <c r="C52" s="7">
         <v>0</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -1954,7 +1963,7 @@
       <c r="B53" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C53" s="6">
+      <c r="C53" s="7">
         <v>0</v>
       </c>
       <c r="D53" s="6" t="s">
@@ -1968,7 +1977,7 @@
       <c r="B54" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C54" s="7">
         <v>0</v>
       </c>
       <c r="D54" s="6" t="s">
@@ -1982,7 +1991,7 @@
       <c r="B55" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C55" s="7">
         <v>0</v>
       </c>
       <c r="D55" s="6" t="s">
@@ -1996,7 +2005,7 @@
       <c r="B56" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="6">
+      <c r="C56" s="7">
         <v>0</v>
       </c>
       <c r="D56" s="6" t="s">
@@ -2010,7 +2019,7 @@
       <c r="B57" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="6">
+      <c r="C57" s="7">
         <v>0</v>
       </c>
       <c r="D57" s="6" t="s">
@@ -2024,7 +2033,7 @@
       <c r="B58" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C58" s="6">
+      <c r="C58" s="7">
         <v>0</v>
       </c>
       <c r="D58" s="6" t="s">
@@ -2038,7 +2047,7 @@
       <c r="B59" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="7">
         <v>0</v>
       </c>
       <c r="D59" s="6" t="s">
@@ -2052,7 +2061,7 @@
       <c r="B60" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C60" s="6">
+      <c r="C60" s="7">
         <v>0</v>
       </c>
       <c r="D60" s="6" t="s">
@@ -2066,7 +2075,7 @@
       <c r="B61" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C61" s="6">
+      <c r="C61" s="7">
         <v>0</v>
       </c>
       <c r="D61" s="6" t="s">
@@ -2080,7 +2089,7 @@
       <c r="B62" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="6">
+      <c r="C62" s="7">
         <v>0</v>
       </c>
       <c r="D62" s="6" t="s">
@@ -2094,7 +2103,7 @@
       <c r="B63" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C63" s="6">
+      <c r="C63" s="7">
         <v>0</v>
       </c>
       <c r="D63" s="6" t="s">
@@ -2108,7 +2117,7 @@
       <c r="B64" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C64" s="6">
+      <c r="C64" s="7">
         <v>0</v>
       </c>
       <c r="D64" s="6" t="s">
@@ -2122,7 +2131,7 @@
       <c r="B65" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C65" s="6">
+      <c r="C65" s="7">
         <v>0</v>
       </c>
       <c r="D65" s="6" t="s">
@@ -2136,7 +2145,7 @@
       <c r="B66" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C66" s="6">
+      <c r="C66" s="7">
         <v>0</v>
       </c>
       <c r="D66" s="6" t="s">
@@ -2150,7 +2159,7 @@
       <c r="B67" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C67" s="6">
+      <c r="C67" s="7">
         <v>0</v>
       </c>
       <c r="D67" s="6" t="s">
@@ -2164,7 +2173,7 @@
       <c r="B68" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C68" s="6">
+      <c r="C68" s="7">
         <v>0</v>
       </c>
       <c r="D68" s="6" t="s">
@@ -2178,7 +2187,7 @@
       <c r="B69" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C69" s="6">
+      <c r="C69" s="7">
         <v>0</v>
       </c>
       <c r="D69" s="6" t="s">
@@ -2192,7 +2201,7 @@
       <c r="B70" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C70" s="6">
+      <c r="C70" s="7">
         <v>0</v>
       </c>
       <c r="D70" s="6" t="s">
@@ -2206,7 +2215,7 @@
       <c r="B71" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C71" s="6">
+      <c r="C71" s="7">
         <v>0</v>
       </c>
       <c r="D71" s="6" t="s">
@@ -2220,7 +2229,7 @@
       <c r="B72" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C72" s="6">
+      <c r="C72" s="7">
         <v>0</v>
       </c>
       <c r="D72" s="6" t="s">
@@ -2234,7 +2243,7 @@
       <c r="B73" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C73" s="6">
+      <c r="C73" s="7">
         <v>0</v>
       </c>
       <c r="D73" s="6" t="s">
@@ -2248,7 +2257,7 @@
       <c r="B74" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C74" s="6">
+      <c r="C74" s="7">
         <v>0</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2262,7 +2271,7 @@
       <c r="B75" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C75" s="6">
+      <c r="C75" s="7">
         <v>0</v>
       </c>
       <c r="D75" s="6" t="s">
@@ -2276,7 +2285,7 @@
       <c r="B76" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C76" s="6">
+      <c r="C76" s="7">
         <v>0</v>
       </c>
       <c r="D76" s="6" t="s">
@@ -2290,7 +2299,7 @@
       <c r="B77" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C77" s="6">
+      <c r="C77" s="7">
         <v>0</v>
       </c>
       <c r="D77" s="6" t="s">
@@ -2304,7 +2313,7 @@
       <c r="B78" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C78" s="6">
+      <c r="C78" s="7">
         <v>0</v>
       </c>
       <c r="D78" s="6" t="s">
@@ -2318,7 +2327,7 @@
       <c r="B79" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C79" s="6">
+      <c r="C79" s="7">
         <v>0</v>
       </c>
       <c r="D79" s="6" t="s">
@@ -2332,7 +2341,7 @@
       <c r="B80" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C80" s="6">
+      <c r="C80" s="7">
         <v>0</v>
       </c>
       <c r="D80" s="6" t="s">
@@ -2346,7 +2355,7 @@
       <c r="B81" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C81" s="6">
+      <c r="C81" s="7">
         <v>0</v>
       </c>
       <c r="D81" s="6" t="s">
@@ -2360,7 +2369,7 @@
       <c r="B82" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C82" s="6">
+      <c r="C82" s="7">
         <v>0</v>
       </c>
       <c r="D82" s="6" t="s">
@@ -2374,7 +2383,7 @@
       <c r="B83" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C83" s="6">
+      <c r="C83" s="7">
         <v>0</v>
       </c>
       <c r="D83" s="6" t="s">
@@ -2388,7 +2397,7 @@
       <c r="B84" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C84" s="6">
+      <c r="C84" s="7">
         <v>0</v>
       </c>
       <c r="D84" s="6" t="s">
@@ -2402,7 +2411,7 @@
       <c r="B85" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C85" s="6">
+      <c r="C85" s="7">
         <v>0</v>
       </c>
       <c r="D85" s="6" t="s">
@@ -2416,7 +2425,7 @@
       <c r="B86" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C86" s="6">
+      <c r="C86" s="7">
         <v>0</v>
       </c>
       <c r="D86" s="6" t="s">
@@ -2430,7 +2439,7 @@
       <c r="B87" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="7">
         <v>0</v>
       </c>
       <c r="D87" s="6" t="s">
@@ -2444,7 +2453,7 @@
       <c r="B88" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C88" s="6">
+      <c r="C88" s="7">
         <v>0</v>
       </c>
       <c r="D88" s="6" t="s">
@@ -2458,7 +2467,7 @@
       <c r="B89" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C89" s="6">
+      <c r="C89" s="7">
         <v>0</v>
       </c>
       <c r="D89" s="6" t="s">
@@ -2472,7 +2481,7 @@
       <c r="B90" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C90" s="6">
+      <c r="C90" s="7">
         <v>0</v>
       </c>
       <c r="D90" s="6" t="s">
@@ -2486,7 +2495,7 @@
       <c r="B91" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C91" s="6">
+      <c r="C91" s="7">
         <v>0</v>
       </c>
       <c r="D91" s="6" t="s">
@@ -2500,7 +2509,7 @@
       <c r="B92" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C92" s="6">
+      <c r="C92" s="7">
         <v>0</v>
       </c>
       <c r="D92" s="6" t="s">
@@ -2514,7 +2523,7 @@
       <c r="B93" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C93" s="6">
+      <c r="C93" s="7">
         <v>0</v>
       </c>
       <c r="D93" s="6" t="s">
@@ -2528,7 +2537,7 @@
       <c r="B94" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C94" s="6">
+      <c r="C94" s="7">
         <v>0</v>
       </c>
       <c r="D94" s="6" t="s">
@@ -2542,7 +2551,7 @@
       <c r="B95" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C95" s="6">
+      <c r="C95" s="7">
         <v>0</v>
       </c>
       <c r="D95" s="6" t="s">
@@ -2556,7 +2565,7 @@
       <c r="B96" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C96" s="6">
+      <c r="C96" s="7">
         <v>0</v>
       </c>
       <c r="D96" s="6" t="s">
@@ -2570,7 +2579,7 @@
       <c r="B97" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C97" s="6">
+      <c r="C97" s="7">
         <v>0</v>
       </c>
       <c r="D97" s="6" t="s">
@@ -2584,7 +2593,7 @@
       <c r="B98" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C98" s="6">
+      <c r="C98" s="7">
         <v>0</v>
       </c>
       <c r="D98" s="6" t="s">
@@ -2598,7 +2607,7 @@
       <c r="B99" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C99" s="6">
+      <c r="C99" s="7">
         <v>0</v>
       </c>
       <c r="D99" s="6" t="s">
@@ -2612,7 +2621,7 @@
       <c r="B100" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C100" s="6">
+      <c r="C100" s="7">
         <v>0</v>
       </c>
       <c r="D100" s="6" t="s">
@@ -2626,7 +2635,7 @@
       <c r="B101" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C101" s="6">
+      <c r="C101" s="7">
         <v>0</v>
       </c>
       <c r="D101" s="6" t="s">
@@ -2640,7 +2649,7 @@
       <c r="B102" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C102" s="6">
+      <c r="C102" s="7">
         <v>0</v>
       </c>
       <c r="D102" s="6" t="s">
@@ -2654,7 +2663,7 @@
       <c r="B103" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C103" s="6">
+      <c r="C103" s="7">
         <v>0</v>
       </c>
       <c r="D103" s="6" t="s">
@@ -2668,7 +2677,7 @@
       <c r="B104" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C104" s="6">
+      <c r="C104" s="7">
         <v>0</v>
       </c>
       <c r="D104" s="6" t="s">
@@ -2682,7 +2691,7 @@
       <c r="B105" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C105" s="6">
+      <c r="C105" s="7">
         <v>0</v>
       </c>
       <c r="D105" s="6" t="s">
@@ -2696,7 +2705,7 @@
       <c r="B106" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C106" s="6">
+      <c r="C106" s="7">
         <v>0</v>
       </c>
       <c r="D106" s="6" t="s">
@@ -2710,7 +2719,7 @@
       <c r="B107" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C107" s="6">
+      <c r="C107" s="7">
         <v>0</v>
       </c>
       <c r="D107" s="6" t="s">
@@ -2724,7 +2733,7 @@
       <c r="B108" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C108" s="6">
+      <c r="C108" s="7">
         <v>0</v>
       </c>
       <c r="D108" s="6" t="s">
@@ -2738,7 +2747,7 @@
       <c r="B109" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C109" s="6">
+      <c r="C109" s="7">
         <v>0</v>
       </c>
       <c r="D109" s="6" t="s">
@@ -2752,7 +2761,7 @@
       <c r="B110" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C110" s="6">
+      <c r="C110" s="7">
         <v>0</v>
       </c>
       <c r="D110" s="6" t="s">
@@ -2766,7 +2775,7 @@
       <c r="B111" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C111" s="6">
+      <c r="C111" s="7">
         <v>0</v>
       </c>
       <c r="D111" s="6" t="s">
@@ -2780,7 +2789,7 @@
       <c r="B112" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C112" s="6">
+      <c r="C112" s="7">
         <v>0</v>
       </c>
       <c r="D112" s="6" t="s">
@@ -2794,7 +2803,7 @@
       <c r="B113" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="7">
         <v>0</v>
       </c>
       <c r="D113" s="6" t="s">
@@ -2808,7 +2817,7 @@
       <c r="B114" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="7">
         <v>0</v>
       </c>
       <c r="D114" s="6" t="s">
@@ -2822,7 +2831,7 @@
       <c r="B115" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="7">
         <v>0</v>
       </c>
       <c r="D115" s="6" t="s">
@@ -2836,7 +2845,7 @@
       <c r="B116" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="7">
         <v>0</v>
       </c>
       <c r="D116" s="6" t="s">
@@ -2850,7 +2859,7 @@
       <c r="B117" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="7">
         <v>0</v>
       </c>
       <c r="D117" s="6" t="s">
@@ -2864,7 +2873,7 @@
       <c r="B118" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C118" s="6">
+      <c r="C118" s="7">
         <v>0</v>
       </c>
       <c r="D118" s="6" t="s">
@@ -2878,7 +2887,7 @@
       <c r="B119" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="7">
         <v>0</v>
       </c>
       <c r="D119" s="6" t="s">
@@ -2892,7 +2901,7 @@
       <c r="B120" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="7">
         <v>0</v>
       </c>
       <c r="D120" s="6" t="s">
@@ -2906,7 +2915,7 @@
       <c r="B121" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="7">
         <v>0</v>
       </c>
       <c r="D121" s="6" t="s">
@@ -2920,7 +2929,7 @@
       <c r="B122" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="7">
         <v>0</v>
       </c>
       <c r="D122" s="6" t="s">
@@ -2934,7 +2943,7 @@
       <c r="B123" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="7">
         <v>0</v>
       </c>
       <c r="D123" s="6" t="s">
@@ -2948,7 +2957,7 @@
       <c r="B124" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="7">
         <v>0</v>
       </c>
       <c r="D124" s="6" t="s">
@@ -2962,7 +2971,7 @@
       <c r="B125" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="7">
         <v>0</v>
       </c>
       <c r="D125" s="6" t="s">
